--- a/Берта Эллинг/12_Смета/БЭ-СМ Смета эллинга — 3 сценария.xlsx
+++ b/Берта Эллинг/12_Смета/БЭ-СМ Смета эллинга — 3 сценария.xlsx
@@ -500,7 +500,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Площадь помещений 961.54 м²; цены Москва/МО под ключ; формулы живые — меняйте цены на листах сценариев</t>
+          <t>Площадь помещений 956.76 м²; цены Москва/МО под ключ; формулы живые — меняйте цены на листах сценариев</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -542,15 +542,15 @@
         </is>
       </c>
       <c r="B5" s="4">
-        <f>'Смета A'!H79</f>
+        <f>'Смета A'!H80</f>
         <v/>
       </c>
       <c r="C5" s="4">
-        <f>'Смета B'!H79</f>
+        <f>'Смета B'!H80</f>
         <v/>
       </c>
       <c r="D5" s="4">
-        <f>'Смета C'!H79</f>
+        <f>'Смета C'!H80</f>
         <v/>
       </c>
     </row>
@@ -561,15 +561,15 @@
         </is>
       </c>
       <c r="B6" s="4">
-        <f>SUM('Вне СМР'!C2:C16)</f>
+        <f>SUM('Вне СМР'!C2:C17)</f>
         <v/>
       </c>
       <c r="C6" s="4">
-        <f>SUM('Вне СМР'!D2:D16)</f>
+        <f>SUM('Вне СМР'!D2:D17)</f>
         <v/>
       </c>
       <c r="D6" s="4">
-        <f>SUM('Вне СМР'!E2:E16)</f>
+        <f>SUM('Вне СМР'!E2:E17)</f>
         <v/>
       </c>
     </row>
@@ -634,15 +634,15 @@
         </is>
       </c>
       <c r="B10" s="4">
-        <f>B5/961.54</f>
+        <f>B5/956.76</f>
         <v/>
       </c>
       <c r="C10" s="4">
-        <f>C5/961.54</f>
+        <f>C5/956.76</f>
         <v/>
       </c>
       <c r="D10" s="4">
-        <f>D5/961.54</f>
+        <f>D5/956.76</f>
         <v/>
       </c>
     </row>
@@ -653,15 +653,15 @@
         </is>
       </c>
       <c r="B11" s="4">
-        <f>B9/961.54</f>
+        <f>B9/956.76</f>
         <v/>
       </c>
       <c r="C11" s="4">
-        <f>C9/961.54</f>
+        <f>C9/956.76</f>
         <v/>
       </c>
       <c r="D11" s="4">
-        <f>D9/961.54</f>
+        <f>D9/956.76</f>
         <v/>
       </c>
     </row>
@@ -728,7 +728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I79"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Сваи ЖБ С80.30 (8 м) с забивкой, 77 шт.</t>
+          <t>Сваи ЖБ С80.30 (8 м) с забивкой, 82 шт.</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>34000</v>
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>513.5700000000001</v>
+        <v>513.1900000000001</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>750</v>
@@ -1166,7 +1166,7 @@
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>1100</v>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>154.1</v>
+        <v>154</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>27000</v>
@@ -1286,7 +1286,7 @@
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>513.5700000000001</v>
+        <v>513.1900000000001</v>
       </c>
       <c r="E14" s="4" t="n">
         <v>7800</v>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Колонны 1 этажа: стальные с огнезащитой R150 (A) / монолит ЖБ 400×400 (B, C)</t>
+          <t>Колонны 1 этажа: стальные по ЭП с огнезащитой R150 (A) / монолит ЖБ 400×400 (B, C)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>R150 для стали — 1,5–3 тыс./м² поверхности; ЖБ обеспечивает сам</t>
+          <t>в ЭП — металл; R150 для стали — 1,5–3 тыс./м² поверхности; ЖБ обеспечивает сам</t>
         </is>
       </c>
     </row>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Межэтажное и под плоскую кровлю: монолит ЖБ плита 200 + рёбра 600 (A, B) / ПБ + монолитные участки (C)</t>
+          <t>Перекрытие 1 этажа и под плоскую кровлю: монолит ЖБ ребристое, плита 250/200 (A, B) / ПБ + монолитные участки (C)</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1406,10 +1406,10 @@
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>798.74</v>
+        <v>945.59</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>11500</v>
+        <v>12000</v>
       </c>
       <c r="F17" s="4">
         <f>H17*0.55</f>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>монолит 10,5–12,5 тыс.; ПБ 5,5–7 тыс.</t>
+          <t>по ЭП 660,5 м² плиты 250 + 285,1 м² плиты 200; монолит 10,5–12,5 тыс.</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>798.74</v>
+        <v>945.59</v>
       </c>
       <c r="E18" s="4" t="n">
         <v>900</v>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Наружные стены газобетон D500 400 мм (блок, клей, армирование, кладка)</t>
+          <t>Наружные стены газобетон D400 400 мм (блок, клей, армирование, кладка)</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>309.14</v>
+        <v>257.56</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>13500</v>
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>153.54</v>
+        <v>147.21</v>
       </c>
       <c r="E22" s="4" t="n">
         <v>13500</v>
@@ -1646,7 +1646,7 @@
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>57.47</v>
+        <v>44.25</v>
       </c>
       <c r="E23" s="4" t="n">
         <v>15000</v>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>473.73</v>
+        <v>353.6</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>7200</v>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Скатная кровля: стропила, ОСП, мембраны, кликфальц, водосток, снегозадержание</t>
+          <t>Скатная кровля 10°: стропила, ОСП, мембраны, Кликфальц Pro, водосток, снегозадержание</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>570.9299999999999</v>
+        <v>448.03</v>
       </c>
       <c r="E26" s="4" t="n">
         <v>11500</v>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Плоская кровля: эксплуатируемая (A, B) / неэксплуатируемая (C)</t>
+          <t>Плоская кровля неэксплуатируемая: уклоны, утепление XPS 200, мембрана, примыкания</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1806,10 +1806,10 @@
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>233.34</v>
+        <v>339.91</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>13300</v>
+        <v>8500</v>
       </c>
       <c r="F27" s="4">
         <f>H27*0.6</f>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>рынок 9–16 тыс.</t>
+          <t>по ЭП — неэксплуатируемая; рынок 7–10 тыс.</t>
         </is>
       </c>
     </row>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Каркасные фронтоны</t>
+          <t>Каркасные стены чердака (фронтоны) 200 мм с фальцем</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>186.21</v>
+        <v>51.72</v>
       </c>
       <c r="E28" s="4" t="n">
         <v>5500</v>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Ворота гаражные секционные утеплённые с автоматикой 3.5×2.6 м</t>
+          <t>Ворота гаражные секционные утеплённые с автоматикой (одинарные боксы) 3,5×2,6 м</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>260000</v>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Ворота эллинга подъёмно-секционные (под катер на прицепе) 4.5×3.6 м</t>
+          <t>Ворота гаражные секционные утеплённые с автоматикой (двойные боксы 004, 009) 5,5×2,6 м</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2326,10 +2326,10 @@
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>650000</v>
+        <v>380000</v>
       </c>
       <c r="F40" s="4">
         <f>H40*0.85</f>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>нестандарт, усиленный привод</t>
+          <t>широкие, с приводом</t>
         </is>
       </c>
     </row>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Двери наружные металлические утеплённые</t>
+          <t>Ворота эллинга подъёмно-секционные (два катера на прицепах) 5,5×3,6 м</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>75000</v>
+        <v>700000</v>
       </c>
       <c r="F41" s="4">
-        <f>H41*0.8</f>
+        <f>H41*0.85</f>
         <v/>
       </c>
       <c r="G41" s="4">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>рынок МО</t>
+          <t>нестандарт, усиленный привод</t>
         </is>
       </c>
     </row>
@@ -2397,19 +2397,19 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Входная группа КПП (алюминий, домофон, доводчик)</t>
+          <t>Двери наружные металлические утеплённые</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>компл</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>350000</v>
+        <v>75000</v>
       </c>
       <c r="F42" s="4">
         <f>H42*0.8</f>
@@ -2432,12 +2432,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>09 Наружные МК</t>
+          <t>08 Окна, витражи, ворота</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Наружная эвакуационная лестница 3-го типа со 2 этажа</t>
+          <t>Входная группа КПП (алюминий, домофон, доводчик)</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2449,10 +2449,10 @@
         <v>1</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>950000</v>
+        <v>350000</v>
       </c>
       <c r="F43" s="4">
-        <f>H43*0.7</f>
+        <f>H43*0.8</f>
         <v/>
       </c>
       <c r="G43" s="4">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>второй эвакуационный выход Ф1.2</t>
+          <t>рынок МО</t>
         </is>
       </c>
     </row>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Навесы, ограждения эксплуатируемой кровли, козырьки</t>
+          <t>Наружная эвакуационная лестница 3-го типа со 2 этажа</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2489,7 +2489,7 @@
         <v>1</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>2200000</v>
+        <v>950000</v>
       </c>
       <c r="F44" s="4">
         <f>H44*0.7</f>
@@ -2505,34 +2505,34 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>без спецификации — по ведомости архитектора</t>
+          <t>второй эвакуационный выход Ф1.2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>10 Отделка черновая</t>
+          <t>09 Наружные МК</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Техзона: упрочнённый пол (топпинг), обеспыливание стен и потолков, покраска</t>
+          <t>Навесы, козырьки, ограждения перехода и наружной лестницы</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>компл</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>379.01</v>
+        <v>1</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>11400</v>
+        <v>1800000</v>
       </c>
       <c r="F45" s="4">
-        <f>H45*0.45</f>
+        <f>H45*0.7</f>
         <v/>
       </c>
       <c r="G45" s="4">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>A — единая ставка ЭП-сметы</t>
+          <t>без спецификации — по ведомости архитектора</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Служебные, проживание, МОП: стяжка, штукатурка, ГКЛ, подготовка</t>
+          <t>Техзона: упрочнённый пол (топпинг), обеспыливание стен и потолков, покраска</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>473.38</v>
+        <v>382.32</v>
       </c>
       <c r="E46" s="4" t="n">
         <v>11400</v>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>рынок 8–14 тыс.</t>
+          <t>A — единая ставка ЭП-сметы</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Спортзал: стяжка с виброразвязкой, акустическая подготовка</t>
+          <t>Служебные, проживание, МОП: стяжка, штукатурка, ГКЛ, подготовка</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2606,13 +2606,13 @@
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>109.15</v>
+        <v>459.96</v>
       </c>
       <c r="E47" s="4" t="n">
         <v>11400</v>
       </c>
       <c r="F47" s="4">
-        <f>H47*0.5</f>
+        <f>H47*0.45</f>
         <v/>
       </c>
       <c r="G47" s="4">
@@ -2625,19 +2625,19 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>свободные веса</t>
+          <t>рынок 8–14 тыс.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>11 Отделка чистовая</t>
+          <t>10 Отделка черновая</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Техзона: разметка, отбойники, полимерные полы в эллинге и котельной</t>
+          <t>Спортзал: стяжка с виброразвязкой, акустическая подготовка</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2646,13 +2646,13 @@
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>379.01</v>
+        <v>114.48</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>23850</v>
+        <v>11400</v>
       </c>
       <c r="F48" s="4">
-        <f>H48*0.6</f>
+        <f>H48*0.5</f>
         <v/>
       </c>
       <c r="G48" s="4">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>A — единая ставка ЭП</t>
+          <t>свободные веса</t>
         </is>
       </c>
     </row>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Служебные и проживание: кварцвинил, керамогранит в с/у, покраска, Армстронг/натяжные, межкомнатные двери</t>
+          <t>Техзона: разметка, отбойники, полимерные полы в эллинге и котельной</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2686,7 +2686,7 @@
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>473.38</v>
+        <v>382.32</v>
       </c>
       <c r="E49" s="4" t="n">
         <v>23850</v>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>минимальный стандарт — решение 05.10; C — shell &amp; core</t>
+          <t>A — единая ставка ЭП</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Спортзал: спортивное покрытие, акустика, зеркала, раздевалка</t>
+          <t>Служебные и проживание: кварцвинил, керамогранит в с/у, покраска, Армстронг/натяжные, межкомнатные двери</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2726,13 +2726,13 @@
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>109.15</v>
+        <v>459.96</v>
       </c>
       <c r="E50" s="4" t="n">
         <v>23850</v>
       </c>
       <c r="F50" s="4">
-        <f>H50*0.65</f>
+        <f>H50*0.6</f>
         <v/>
       </c>
       <c r="G50" s="4">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>по ТЗ интересантов, без лимита</t>
+          <t>минимальный стандарт — решение 05.10; C — shell &amp; core</t>
         </is>
       </c>
     </row>
@@ -2757,22 +2757,22 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Внутренние ограждения, поручни, техметаллоизделия</t>
+          <t>Спортзал: спортивное покрытие, акустика, зеркала, раздевалка</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>компл</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>1</v>
+        <v>114.48</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>2000000</v>
+        <v>23850</v>
       </c>
       <c r="F51" s="4">
-        <f>H51*0.7</f>
+        <f>H51*0.65</f>
         <v/>
       </c>
       <c r="G51" s="4">
@@ -2785,19 +2785,19 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>рынок МО</t>
+          <t>по ТЗ интересантов, без лимита</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>12 Отопление (ОВ)</t>
+          <t>11 Отделка чистовая</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Котельная: пеллетный котёл 60 кВт + бункер, электрокотёл 24 кВт, буфер 1 000 л, обвязка, автоматика (Qрасч ≈ 61 кВт)</t>
+          <t>Внутренние ограждения, поручни, техметаллоизделия</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -2809,10 +2809,10 @@
         <v>1</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>2600000</v>
+        <v>2000000</v>
       </c>
       <c r="F52" s="4">
-        <f>H52*0.75</f>
+        <f>H52*0.7</f>
         <v/>
       </c>
       <c r="G52" s="4">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>аналог 291-ОВ «Ромарио»</t>
+          <t>рынок МО</t>
         </is>
       </c>
     </row>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Дымоход нержавеющий утеплённый Ø200, h ≈ 11 м</t>
+          <t>Котельная: пеллетный котёл 60 кВт + бункер, электрокотёл 24 кВт, буфер 1 000 л, обвязка, автоматика (Qрасч ≈ 62 кВт)</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -2849,7 +2849,7 @@
         <v>1</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>280000</v>
+        <v>2600000</v>
       </c>
       <c r="F53" s="4">
         <f>H53*0.75</f>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>рынок</t>
+          <t>аналог 291-ОВ «Ромарио»</t>
         </is>
       </c>
     </row>
@@ -2877,22 +2877,22 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Тёплые полы водяные: проживание, МОП, спортзал</t>
+          <t>Дымоход нержавеющий утеплённый Ø200, h ≈ 11 м</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>компл</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>522.53</v>
+        <v>1</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>2600</v>
+        <v>280000</v>
       </c>
       <c r="F54" s="4">
-        <f>H54*0.5</f>
+        <f>H54*0.75</f>
         <v/>
       </c>
       <c r="G54" s="4">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>рынок МО</t>
+          <t>рынок</t>
         </is>
       </c>
     </row>
@@ -2917,22 +2917,22 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Конвекторы внутрипольные у витражей, радиаторы в с/у и КПП</t>
+          <t>Тёплые полы водяные: проживание, МОП, спортзал</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>28</v>
+        <v>514.4400000000001</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>45000</v>
+        <v>2600</v>
       </c>
       <c r="F55" s="4">
-        <f>H55*0.75</f>
+        <f>H55*0.5</f>
         <v/>
       </c>
       <c r="G55" s="4">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>рынок</t>
+          <t>рынок МО</t>
         </is>
       </c>
     </row>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Воздушно-отопительные агрегаты гаражей и эллинга (+5 °C)</t>
+          <t>Конвекторы внутрипольные у витражей, радиаторы в с/у и КПП</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>110000</v>
+        <v>45000</v>
       </c>
       <c r="F56" s="4">
         <f>H56*0.75</f>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Volcano/аналог</t>
+          <t>рынок</t>
         </is>
       </c>
     </row>
@@ -2997,22 +2997,22 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Магистрали, коллекторы, изоляция, ПНР</t>
+          <t>Воздушно-отопительные агрегаты гаражей и эллинга (+5 °C)</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>компл</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>1100000</v>
+        <v>110000</v>
       </c>
       <c r="F57" s="4">
-        <f>H57*0.55</f>
+        <f>H57*0.75</f>
         <v/>
       </c>
       <c r="G57" s="4">
@@ -3025,19 +3025,19 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>рынок</t>
+          <t>Volcano/аналог</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>13 Водоснабжение и канализация (ВК)</t>
+          <t>12 Отопление (ОВ)</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Узел ввода, учёт, фильтрация/умягчение</t>
+          <t>Магистрали, коллекторы, изоляция, ПНР</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3049,10 +3049,10 @@
         <v>1</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>450000</v>
+        <v>1100000</v>
       </c>
       <c r="F58" s="4">
-        <f>H58*0.75</f>
+        <f>H58*0.55</f>
         <v/>
       </c>
       <c r="G58" s="4">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>посёлковая сеть</t>
+          <t>рынок</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Бойлер косвенного нагрева 500 л + рециркуляция ГВС</t>
+          <t>Узел ввода, учёт, фильтрация/умягчение</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3089,7 +3089,7 @@
         <v>1</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>380000</v>
+        <v>450000</v>
       </c>
       <c r="F59" s="4">
         <f>H59*0.75</f>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>рынок</t>
+          <t>посёлковая сеть</t>
         </is>
       </c>
     </row>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Внутренние сети В1/Т3/Т4/К1 с изоляцией</t>
+          <t>Бойлер косвенного нагрева 500 л + рециркуляция ГВС</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>компл</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>961.54</v>
+        <v>1</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>1300</v>
+        <v>380000</v>
       </c>
       <c r="F60" s="4">
-        <f>H60*0.5</f>
+        <f>H60*0.75</f>
         <v/>
       </c>
       <c r="G60" s="4">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>рынок МО</t>
+          <t>рынок</t>
         </is>
       </c>
     </row>
@@ -3157,22 +3157,22 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Санузлы: унитаз, раковина, душ/поддон, смесители — 10 шт.</t>
+          <t>Внутренние сети В1/Т3/Т4/К1 с изоляцией</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>10</v>
+        <v>956.76</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>160000</v>
+        <v>1300</v>
       </c>
       <c r="F61" s="4">
-        <f>H61*0.7</f>
+        <f>H61*0.5</f>
         <v/>
       </c>
       <c r="G61" s="4">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>C — только КПП и раздевалка, прочие — точки подключения</t>
+          <t>рынок МО</t>
         </is>
       </c>
     </row>
@@ -3197,22 +3197,22 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Трапы и лотки гаражей/эллинга, бензомаслоуловитель (ЛОС) 1 л/с</t>
+          <t>Санузлы: унитаз, раковина, душ/поддон, смесители — 10 шт.</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>компл</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>650000</v>
+        <v>160000</v>
       </c>
       <c r="F62" s="4">
-        <f>H62*0.75</f>
+        <f>H62*0.7</f>
         <v/>
       </c>
       <c r="G62" s="4">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>ВОЗ — обязательно</t>
+          <t>C — только КПП и раздевалка, прочие — точки подключения</t>
         </is>
       </c>
     </row>
@@ -3237,7 +3237,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Кухня столовой, прачечная: подключение оборудования</t>
+          <t>Трапы и лотки гаражей/эллинга, бензомаслоуловитель (ЛОС) 1 л/с</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3249,10 +3249,10 @@
         <v>1</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>250000</v>
+        <v>650000</v>
       </c>
       <c r="F63" s="4">
-        <f>H63*0.5</f>
+        <f>H63*0.75</f>
         <v/>
       </c>
       <c r="G63" s="4">
@@ -3265,19 +3265,19 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>рынок</t>
+          <t>ВОЗ — обязательно</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>14 Вентиляция и кондиционирование (ОВК)</t>
+          <t>13 Водоснабжение и канализация (ВК)</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>П1/В1 проживание 1 300 м³/ч с рекуператором, воздуховоды, распределители</t>
+          <t>Кухня столовой, прачечная: подключение оборудования</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3289,10 +3289,10 @@
         <v>1</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>2600000</v>
+        <v>250000</v>
       </c>
       <c r="F64" s="4">
-        <f>H64*0.7</f>
+        <f>H64*0.5</f>
         <v/>
       </c>
       <c r="G64" s="4">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>П2/В2 спортзал 1 200 м³/ч с рекуператором и охладителем</t>
+          <t>П1/В1 проживание 1 300 м³/ч с рекуператором, воздуховоды, распределители</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>1900000</v>
+        <v>2600000</v>
       </c>
       <c r="F65" s="4">
         <f>H65*0.7</f>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>по ТЗ спортзала</t>
+          <t>рынок</t>
         </is>
       </c>
     </row>
@@ -3357,7 +3357,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>В3 гаражи и эллинг: вытяжка по датчикам CO/паров, клапаны</t>
+          <t>П2/В2 спортзал 1 200 м³/ч с рекуператором и охладителем</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -3369,7 +3369,7 @@
         <v>1</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>900000</v>
+        <v>1900000</v>
       </c>
       <c r="F66" s="4">
         <f>H66*0.7</f>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>без приточки</t>
+          <t>по ТЗ спортзала</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Кондиционирование: мини-VRF 22 кВт — спортзал, столовая, КПП, охрана</t>
+          <t>В3 гаражи и эллинг: вытяжка по датчикам CO/паров, клапаны</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3409,10 +3409,10 @@
         <v>1</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>3500000</v>
+        <v>900000</v>
       </c>
       <c r="F67" s="4">
-        <f>H67*0.75</f>
+        <f>H67*0.7</f>
         <v/>
       </c>
       <c r="G67" s="4">
@@ -3425,19 +3425,19 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>A — «условно» ЭП</t>
+          <t>без приточки</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>15 Электроснабжение и освещение (ЭОМ)</t>
+          <t>14 Вентиляция и кондиционирование (ОВК)</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>ВРУ/ГРЩ 100 А, учёт, АВР на ДГУ посёлка, щиты этажные</t>
+          <t>Кондиционирование: мини-VRF 22 кВт — спортзал, столовая, КПП, охрана</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3449,7 +3449,7 @@
         <v>1</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>900000</v>
+        <v>3500000</v>
       </c>
       <c r="F68" s="4">
         <f>H68*0.75</f>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>Pр ≈ 60 кВт</t>
+          <t>A — «условно» ЭП</t>
         </is>
       </c>
     </row>
@@ -3477,22 +3477,22 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Кабельные сети, розетки, выключатели, освещение (светильники служебного стандарта)</t>
+          <t>ВРУ/ГРЩ 100 А в электрощитовой 013, учёт, АВР на генератор, щиты этажные</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>компл</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>961.54</v>
+        <v>1</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>4300</v>
+        <v>900000</v>
       </c>
       <c r="F69" s="4">
-        <f>H69*0.55</f>
+        <f>H69*0.75</f>
         <v/>
       </c>
       <c r="G69" s="4">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>A — 6,0 млн ЭП-сметы</t>
+          <t>Pр ≈ 60 кВт</t>
         </is>
       </c>
     </row>
@@ -3517,22 +3517,22 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Освещение спортзала и фасадов (архитектурное, к воде)</t>
+          <t>Кабельные сети, розетки, выключатели, освещение (светильники служебного стандарта)</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>компл</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>1</v>
+        <v>956.76</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>900000</v>
+        <v>4300</v>
       </c>
       <c r="F70" s="4">
-        <f>H70*0.75</f>
+        <f>H70*0.55</f>
         <v/>
       </c>
       <c r="G70" s="4">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>рынок</t>
+          <t>A — 6,0 млн ЭП-сметы</t>
         </is>
       </c>
     </row>
@@ -3557,22 +3557,22 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Зарядные станции 7,4 кВт с управлением нагрузкой</t>
+          <t>Освещение спортзала и фасадов (архитектурное, к воде)</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>компл</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>140000</v>
+        <v>900000</v>
       </c>
       <c r="F71" s="4">
-        <f>H71*0.8</f>
+        <f>H71*0.75</f>
         <v/>
       </c>
       <c r="G71" s="4">
@@ -3585,7 +3585,7 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>C — только кабельные трассы</t>
+          <t>рынок</t>
         </is>
       </c>
     </row>
@@ -3597,22 +3597,22 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Молниезащита, заземление, уравнивание потенциалов</t>
+          <t>Зарядные станции 7,4 кВт с управлением нагрузкой</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>компл</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>500000</v>
+        <v>140000</v>
       </c>
       <c r="F72" s="4">
-        <f>H72*0.6</f>
+        <f>H72*0.8</f>
         <v/>
       </c>
       <c r="G72" s="4">
@@ -3625,31 +3625,31 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>аналог 291-МЗ</t>
+          <t>C — только кабельные трассы</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>16 Слаботочные системы и пожарная безопасность (СС, ПБ)</t>
+          <t>15 Электроснабжение и освещение (ЭОМ)</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>АПС адресная + СОУЭ 2 типа</t>
+          <t>Молниезащита, заземление, уравнивание потенциалов</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>компл</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>961.54</v>
+        <v>1</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>750</v>
+        <v>500000</v>
       </c>
       <c r="F73" s="4">
         <f>H73*0.6</f>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>СП 484, 3.13130</t>
+          <t>аналог 291-МЗ</t>
         </is>
       </c>
     </row>
@@ -3677,22 +3677,22 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Модульное пожаротушение эллинга и котельной (по разделу ПБ)</t>
+          <t>АПС адресная + СОУЭ 2 типа</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>компл</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>1</v>
+        <v>956.76</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>450000</v>
+        <v>750</v>
       </c>
       <c r="F74" s="4">
-        <f>H74*0.8</f>
+        <f>H74*0.6</f>
         <v/>
       </c>
       <c r="G74" s="4">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>опция — проверить в ПБ</t>
+          <t>СП 484, 3.13130</t>
         </is>
       </c>
     </row>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>КПП: СКУД, шлагбаум, распознавание номеров, домофония</t>
+          <t>Модульное пожаротушение эллинга и котельной (по разделу ПБ)</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -3729,10 +3729,10 @@
         <v>1</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>900000</v>
+        <v>450000</v>
       </c>
       <c r="F75" s="4">
-        <f>H75*0.75</f>
+        <f>H75*0.8</f>
         <v/>
       </c>
       <c r="G75" s="4">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>въезд посёлка</t>
+          <t>опция — проверить в ПБ</t>
         </is>
       </c>
     </row>
@@ -3757,7 +3757,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Видеонаблюдение 16 камер + сервер, охранная сигнализация</t>
+          <t>КПП: СКУД, шлагбаум, распознавание номеров, домофония</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>рынок</t>
+          <t>въезд посёлка</t>
         </is>
       </c>
     </row>
@@ -3797,7 +3797,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>СКС, Wi-Fi, стойка, диспетчеризация инженерии (Home Assistant)</t>
+          <t>Видеонаблюдение 16 камер + сервер, охранная сигнализация</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -3812,7 +3812,7 @@
         <v>900000</v>
       </c>
       <c r="F77" s="4">
-        <f>H77*0.7</f>
+        <f>H77*0.75</f>
         <v/>
       </c>
       <c r="G77" s="4">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>аналог 291-СС</t>
+          <t>рынок</t>
         </is>
       </c>
     </row>
@@ -3837,7 +3837,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Пусконаладка всех инженерных систем</t>
+          <t>СКС, Wi-Fi, стойка, диспетчеризация инженерии (Home Assistant)</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -3849,10 +3849,10 @@
         <v>1</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>1000000</v>
+        <v>900000</v>
       </c>
       <c r="F78" s="4">
-        <f>H78*0.0</f>
+        <f>H78*0.7</f>
         <v/>
       </c>
       <c r="G78" s="4">
@@ -3865,33 +3865,73 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
+          <t>аналог 291-СС</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>16 Слаботочные системы и пожарная безопасность (СС, ПБ)</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Пусконаладка всех инженерных систем</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>компл</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" s="4" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F79" s="4">
+        <f>H79*0.0</f>
+        <v/>
+      </c>
+      <c r="G79" s="4">
+        <f>H79-F79</f>
+        <v/>
+      </c>
+      <c r="H79" s="4">
+        <f>D79*E79</f>
+        <v/>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
           <t>рынок</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="6" t="inlineStr"/>
-      <c r="B79" s="6" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr"/>
+      <c r="B80" s="6" t="inlineStr">
         <is>
           <t>ИТОГО СМР</t>
         </is>
       </c>
-      <c r="C79" s="6" t="inlineStr"/>
-      <c r="D79" s="10" t="inlineStr"/>
-      <c r="E79" s="7" t="inlineStr"/>
-      <c r="F79" s="7">
-        <f>SUM(F2:F78)</f>
-        <v/>
-      </c>
-      <c r="G79" s="7">
-        <f>SUM(G2:G78)</f>
-        <v/>
-      </c>
-      <c r="H79" s="7">
-        <f>SUM(H2:H78)</f>
-        <v/>
-      </c>
-      <c r="I79" s="6" t="inlineStr"/>
+      <c r="C80" s="6" t="inlineStr"/>
+      <c r="D80" s="10" t="inlineStr"/>
+      <c r="E80" s="7" t="inlineStr"/>
+      <c r="F80" s="7">
+        <f>SUM(F2:F79)</f>
+        <v/>
+      </c>
+      <c r="G80" s="7">
+        <f>SUM(G2:G79)</f>
+        <v/>
+      </c>
+      <c r="H80" s="7">
+        <f>SUM(H2:H79)</f>
+        <v/>
+      </c>
+      <c r="I80" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3904,7 +3944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I79"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4213,7 +4253,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Сваи ЖБ С80.30 (8 м) с забивкой, 77 шт.</t>
+          <t>Сваи ЖБ С80.30 (8 м) с забивкой, 82 шт.</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -4222,7 +4262,7 @@
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>31000</v>
@@ -4302,7 +4342,7 @@
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>513.5700000000001</v>
+        <v>513.1900000000001</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>700</v>
@@ -4342,7 +4382,7 @@
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>950</v>
@@ -4422,7 +4462,7 @@
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>154.1</v>
+        <v>154</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>25000</v>
@@ -4462,7 +4502,7 @@
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>513.5700000000001</v>
+        <v>513.1900000000001</v>
       </c>
       <c r="E14" s="4" t="n">
         <v>0</v>
@@ -4533,7 +4573,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Колонны 1 этажа: стальные с огнезащитой R150 (A) / монолит ЖБ 400×400 (B, C)</t>
+          <t>Колонны 1 этажа: стальные по ЭП с огнезащитой R150 (A) / монолит ЖБ 400×400 (B, C)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -4561,7 +4601,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>R150 для стали — 1,5–3 тыс./м² поверхности; ЖБ обеспечивает сам</t>
+          <t>в ЭП — металл; R150 для стали — 1,5–3 тыс./м² поверхности; ЖБ обеспечивает сам</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4613,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Межэтажное и под плоскую кровлю: монолит ЖБ плита 200 + рёбра 600 (A, B) / ПБ + монолитные участки (C)</t>
+          <t>Перекрытие 1 этажа и под плоскую кровлю: монолит ЖБ ребристое, плита 250/200 (A, B) / ПБ + монолитные участки (C)</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -4582,10 +4622,10 @@
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>798.74</v>
+        <v>945.59</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>11500</v>
+        <v>11800</v>
       </c>
       <c r="F17" s="4">
         <f>H17*0.55</f>
@@ -4601,7 +4641,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>монолит 10,5–12,5 тыс.; ПБ 5,5–7 тыс.</t>
+          <t>по ЭП 660,5 м² плиты 250 + 285,1 м² плиты 200; монолит 10,5–12,5 тыс.</t>
         </is>
       </c>
     </row>
@@ -4622,7 +4662,7 @@
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>798.74</v>
+        <v>945.59</v>
       </c>
       <c r="E18" s="4" t="n">
         <v>0</v>
@@ -4733,7 +4773,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Наружные стены газобетон D500 400 мм (блок, клей, армирование, кладка)</t>
+          <t>Наружные стены газобетон D400 400 мм (блок, клей, армирование, кладка)</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -4742,7 +4782,7 @@
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>309.14</v>
+        <v>257.56</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>13000</v>
@@ -4782,7 +4822,7 @@
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>153.54</v>
+        <v>147.21</v>
       </c>
       <c r="E22" s="4" t="n">
         <v>13000</v>
@@ -4822,7 +4862,7 @@
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>57.47</v>
+        <v>44.25</v>
       </c>
       <c r="E23" s="4" t="n">
         <v>14000</v>
@@ -4902,7 +4942,7 @@
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>473.73</v>
+        <v>353.6</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>7000</v>
@@ -4933,7 +4973,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Скатная кровля: стропила, ОСП, мембраны, кликфальц, водосток, снегозадержание</t>
+          <t>Скатная кровля 10°: стропила, ОСП, мембраны, Кликфальц Pro, водосток, снегозадержание</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -4942,7 +4982,7 @@
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>570.9299999999999</v>
+        <v>448.03</v>
       </c>
       <c r="E26" s="4" t="n">
         <v>11000</v>
@@ -4973,7 +5013,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Плоская кровля: эксплуатируемая (A, B) / неэксплуатируемая (C)</t>
+          <t>Плоская кровля неэксплуатируемая: уклоны, утепление XPS 200, мембрана, примыкания</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -4982,10 +5022,10 @@
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>233.34</v>
+        <v>339.91</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>12500</v>
+        <v>8000</v>
       </c>
       <c r="F27" s="4">
         <f>H27*0.6</f>
@@ -5001,7 +5041,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>рынок 9–16 тыс.</t>
+          <t>по ЭП — неэксплуатируемая; рынок 7–10 тыс.</t>
         </is>
       </c>
     </row>
@@ -5013,7 +5053,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Каркасные фронтоны</t>
+          <t>Каркасные стены чердака (фронтоны) 200 мм с фальцем</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -5022,7 +5062,7 @@
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>186.21</v>
+        <v>51.72</v>
       </c>
       <c r="E28" s="4" t="n">
         <v>5500</v>
@@ -5453,7 +5493,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Ворота гаражные секционные утеплённые с автоматикой 3.5×2.6 м</t>
+          <t>Ворота гаражные секционные утеплённые с автоматикой (одинарные боксы) 3,5×2,6 м</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -5462,7 +5502,7 @@
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>220000</v>
@@ -5493,7 +5533,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Ворота эллинга подъёмно-секционные (под катер на прицепе) 4.5×3.6 м</t>
+          <t>Ворота гаражные секционные утеплённые с автоматикой (двойные боксы 004, 009) 5,5×2,6 м</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -5502,10 +5542,10 @@
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>520000</v>
+        <v>330000</v>
       </c>
       <c r="F40" s="4">
         <f>H40*0.85</f>
@@ -5521,7 +5561,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>нестандарт, усиленный привод</t>
+          <t>широкие, с приводом</t>
         </is>
       </c>
     </row>
@@ -5533,7 +5573,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Двери наружные металлические утеплённые</t>
+          <t>Ворота эллинга подъёмно-секционные (два катера на прицепах) 5,5×3,6 м</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -5542,13 +5582,13 @@
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>60000</v>
+        <v>580000</v>
       </c>
       <c r="F41" s="4">
-        <f>H41*0.8</f>
+        <f>H41*0.85</f>
         <v/>
       </c>
       <c r="G41" s="4">
@@ -5561,7 +5601,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>рынок МО</t>
+          <t>нестандарт, усиленный привод</t>
         </is>
       </c>
     </row>
@@ -5573,19 +5613,19 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Входная группа КПП (алюминий, домофон, доводчик)</t>
+          <t>Двери наружные металлические утеплённые</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>компл</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>280000</v>
+        <v>60000</v>
       </c>
       <c r="F42" s="4">
         <f>H42*0.8</f>
@@ -5608,12 +5648,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>09 Наружные МК</t>
+          <t>08 Окна, витражи, ворота</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Наружная эвакуационная лестница 3-го типа со 2 этажа</t>
+          <t>Входная группа КПП (алюминий, домофон, доводчик)</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -5625,10 +5665,10 @@
         <v>1</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>850000</v>
+        <v>280000</v>
       </c>
       <c r="F43" s="4">
-        <f>H43*0.7</f>
+        <f>H43*0.8</f>
         <v/>
       </c>
       <c r="G43" s="4">
@@ -5641,7 +5681,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>второй эвакуационный выход Ф1.2</t>
+          <t>рынок МО</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5693,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Навесы, ограждения эксплуатируемой кровли, козырьки</t>
+          <t>Наружная эвакуационная лестница 3-го типа со 2 этажа</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -5665,7 +5705,7 @@
         <v>1</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>1500000</v>
+        <v>850000</v>
       </c>
       <c r="F44" s="4">
         <f>H44*0.7</f>
@@ -5681,34 +5721,34 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>без спецификации — по ведомости архитектора</t>
+          <t>второй эвакуационный выход Ф1.2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>10 Отделка черновая</t>
+          <t>09 Наружные МК</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Техзона: упрочнённый пол (топпинг), обеспыливание стен и потолков, покраска</t>
+          <t>Навесы, козырьки, ограждения перехода и наружной лестницы</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>компл</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>379.01</v>
+        <v>1</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>3800</v>
+        <v>1200000</v>
       </c>
       <c r="F45" s="4">
-        <f>H45*0.45</f>
+        <f>H45*0.7</f>
         <v/>
       </c>
       <c r="G45" s="4">
@@ -5721,7 +5761,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>A — единая ставка ЭП-сметы</t>
+          <t>без спецификации — по ведомости архитектора</t>
         </is>
       </c>
     </row>
@@ -5733,7 +5773,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Служебные, проживание, МОП: стяжка, штукатурка, ГКЛ, подготовка</t>
+          <t>Техзона: упрочнённый пол (топпинг), обеспыливание стен и потолков, покраска</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -5742,10 +5782,10 @@
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>473.38</v>
+        <v>382.32</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>9000</v>
+        <v>3800</v>
       </c>
       <c r="F46" s="4">
         <f>H46*0.45</f>
@@ -5761,7 +5801,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>рынок 8–14 тыс.</t>
+          <t>A — единая ставка ЭП-сметы</t>
         </is>
       </c>
     </row>
@@ -5773,7 +5813,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Спортзал: стяжка с виброразвязкой, акустическая подготовка</t>
+          <t>Служебные, проживание, МОП: стяжка, штукатурка, ГКЛ, подготовка</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -5782,13 +5822,13 @@
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>109.15</v>
+        <v>459.96</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>13000</v>
+        <v>9000</v>
       </c>
       <c r="F47" s="4">
-        <f>H47*0.5</f>
+        <f>H47*0.45</f>
         <v/>
       </c>
       <c r="G47" s="4">
@@ -5801,19 +5841,19 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>свободные веса</t>
+          <t>рынок 8–14 тыс.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>11 Отделка чистовая</t>
+          <t>10 Отделка черновая</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Техзона: разметка, отбойники, полимерные полы в эллинге и котельной</t>
+          <t>Спортзал: стяжка с виброразвязкой, акустическая подготовка</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -5822,13 +5862,13 @@
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>379.01</v>
+        <v>114.48</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>2500</v>
+        <v>13000</v>
       </c>
       <c r="F48" s="4">
-        <f>H48*0.6</f>
+        <f>H48*0.5</f>
         <v/>
       </c>
       <c r="G48" s="4">
@@ -5841,7 +5881,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>A — единая ставка ЭП</t>
+          <t>свободные веса</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5893,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Служебные и проживание: кварцвинил, керамогранит в с/у, покраска, Армстронг/натяжные, межкомнатные двери</t>
+          <t>Техзона: разметка, отбойники, полимерные полы в эллинге и котельной</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -5862,10 +5902,10 @@
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>473.38</v>
+        <v>382.32</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>14000</v>
+        <v>2500</v>
       </c>
       <c r="F49" s="4">
         <f>H49*0.6</f>
@@ -5881,7 +5921,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>минимальный стандарт — решение 05.10; C — shell &amp; core</t>
+          <t>A — единая ставка ЭП</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5933,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Спортзал: спортивное покрытие, акустика, зеркала, раздевалка</t>
+          <t>Служебные и проживание: кварцвинил, керамогранит в с/у, покраска, Армстронг/натяжные, межкомнатные двери</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -5902,13 +5942,13 @@
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>109.15</v>
+        <v>459.96</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>32000</v>
+        <v>14000</v>
       </c>
       <c r="F50" s="4">
-        <f>H50*0.65</f>
+        <f>H50*0.6</f>
         <v/>
       </c>
       <c r="G50" s="4">
@@ -5921,7 +5961,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>по ТЗ интересантов, без лимита</t>
+          <t>минимальный стандарт — решение 05.10; C — shell &amp; core</t>
         </is>
       </c>
     </row>
@@ -5933,22 +5973,22 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Внутренние ограждения, поручни, техметаллоизделия</t>
+          <t>Спортзал: спортивное покрытие, акустика, зеркала, раздевалка</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>компл</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>1</v>
+        <v>114.48</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>1200000</v>
+        <v>32000</v>
       </c>
       <c r="F51" s="4">
-        <f>H51*0.7</f>
+        <f>H51*0.65</f>
         <v/>
       </c>
       <c r="G51" s="4">
@@ -5961,19 +6001,19 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>рынок МО</t>
+          <t>по ТЗ интересантов, без лимита</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>12 Отопление (ОВ)</t>
+          <t>11 Отделка чистовая</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Котельная: пеллетный котёл 60 кВт + бункер, электрокотёл 24 кВт, буфер 1 000 л, обвязка, автоматика (Qрасч ≈ 61 кВт)</t>
+          <t>Внутренние ограждения, поручни, техметаллоизделия</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -5985,10 +6025,10 @@
         <v>1</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>2300000</v>
+        <v>1200000</v>
       </c>
       <c r="F52" s="4">
-        <f>H52*0.75</f>
+        <f>H52*0.7</f>
         <v/>
       </c>
       <c r="G52" s="4">
@@ -6001,7 +6041,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>аналог 291-ОВ «Ромарио»</t>
+          <t>рынок МО</t>
         </is>
       </c>
     </row>
@@ -6013,7 +6053,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Дымоход нержавеющий утеплённый Ø200, h ≈ 11 м</t>
+          <t>Котельная: пеллетный котёл 60 кВт + бункер, электрокотёл 24 кВт, буфер 1 000 л, обвязка, автоматика (Qрасч ≈ 62 кВт)</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -6025,7 +6065,7 @@
         <v>1</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>250000</v>
+        <v>2300000</v>
       </c>
       <c r="F53" s="4">
         <f>H53*0.75</f>
@@ -6041,7 +6081,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>рынок</t>
+          <t>аналог 291-ОВ «Ромарио»</t>
         </is>
       </c>
     </row>
@@ -6053,22 +6093,22 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Тёплые полы водяные: проживание, МОП, спортзал</t>
+          <t>Дымоход нержавеющий утеплённый Ø200, h ≈ 11 м</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>компл</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>522.53</v>
+        <v>1</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>2300</v>
+        <v>250000</v>
       </c>
       <c r="F54" s="4">
-        <f>H54*0.5</f>
+        <f>H54*0.75</f>
         <v/>
       </c>
       <c r="G54" s="4">
@@ -6081,7 +6121,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>рынок МО</t>
+          <t>рынок</t>
         </is>
       </c>
     </row>
@@ -6093,22 +6133,22 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Конвекторы внутрипольные у витражей, радиаторы в с/у и КПП</t>
+          <t>Тёплые полы водяные: проживание, МОП, спортзал</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>28</v>
+        <v>514.4400000000001</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>32000</v>
+        <v>2300</v>
       </c>
       <c r="F55" s="4">
-        <f>H55*0.75</f>
+        <f>H55*0.5</f>
         <v/>
       </c>
       <c r="G55" s="4">
@@ -6121,7 +6161,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>рынок</t>
+          <t>рынок МО</t>
         </is>
       </c>
     </row>
@@ -6133,7 +6173,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Воздушно-отопительные агрегаты гаражей и эллинга (+5 °C)</t>
+          <t>Конвекторы внутрипольные у витражей, радиаторы в с/у и КПП</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -6142,10 +6182,10 @@
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>95000</v>
+        <v>32000</v>
       </c>
       <c r="F56" s="4">
         <f>H56*0.75</f>
@@ -6161,7 +6201,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Volcano/аналог</t>
+          <t>рынок</t>
         </is>
       </c>
     </row>
@@ -6173,22 +6213,22 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Магистрали, коллекторы, изоляция, ПНР</t>
+          <t>Воздушно-отопительные агрегаты гаражей и эллинга (+5 °C)</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>компл</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>900000</v>
+        <v>95000</v>
       </c>
       <c r="F57" s="4">
-        <f>H57*0.55</f>
+        <f>H57*0.75</f>
         <v/>
       </c>
       <c r="G57" s="4">
@@ -6201,19 +6241,19 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>рынок</t>
+          <t>Volcano/аналог</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>13 Водоснабжение и канализация (ВК)</t>
+          <t>12 Отопление (ОВ)</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Узел ввода, учёт, фильтрация/умягчение</t>
+          <t>Магистрали, коллекторы, изоляция, ПНР</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -6225,10 +6265,10 @@
         <v>1</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>380000</v>
+        <v>900000</v>
       </c>
       <c r="F58" s="4">
-        <f>H58*0.75</f>
+        <f>H58*0.55</f>
         <v/>
       </c>
       <c r="G58" s="4">
@@ -6241,7 +6281,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>посёлковая сеть</t>
+          <t>рынок</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6293,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Бойлер косвенного нагрева 500 л + рециркуляция ГВС</t>
+          <t>Узел ввода, учёт, фильтрация/умягчение</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -6265,7 +6305,7 @@
         <v>1</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>330000</v>
+        <v>380000</v>
       </c>
       <c r="F59" s="4">
         <f>H59*0.75</f>
@@ -6281,7 +6321,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>рынок</t>
+          <t>посёлковая сеть</t>
         </is>
       </c>
     </row>
@@ -6293,22 +6333,22 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Внутренние сети В1/Т3/Т4/К1 с изоляцией</t>
+          <t>Бойлер косвенного нагрева 500 л + рециркуляция ГВС</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>компл</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>961.54</v>
+        <v>1</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>1100</v>
+        <v>330000</v>
       </c>
       <c r="F60" s="4">
-        <f>H60*0.5</f>
+        <f>H60*0.75</f>
         <v/>
       </c>
       <c r="G60" s="4">
@@ -6321,7 +6361,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>рынок МО</t>
+          <t>рынок</t>
         </is>
       </c>
     </row>
@@ -6333,22 +6373,22 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Санузлы: унитаз, раковина, душ/поддон, смесители — 10 шт.</t>
+          <t>Внутренние сети В1/Т3/Т4/К1 с изоляцией</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>10</v>
+        <v>956.76</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>110000</v>
+        <v>1100</v>
       </c>
       <c r="F61" s="4">
-        <f>H61*0.7</f>
+        <f>H61*0.5</f>
         <v/>
       </c>
       <c r="G61" s="4">
@@ -6361,7 +6401,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>C — только КПП и раздевалка, прочие — точки подключения</t>
+          <t>рынок МО</t>
         </is>
       </c>
     </row>
@@ -6373,22 +6413,22 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Трапы и лотки гаражей/эллинга, бензомаслоуловитель (ЛОС) 1 л/с</t>
+          <t>Санузлы: унитаз, раковина, душ/поддон, смесители — 10 шт.</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>компл</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>600000</v>
+        <v>110000</v>
       </c>
       <c r="F62" s="4">
-        <f>H62*0.75</f>
+        <f>H62*0.7</f>
         <v/>
       </c>
       <c r="G62" s="4">
@@ -6401,7 +6441,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>ВОЗ — обязательно</t>
+          <t>C — только КПП и раздевалка, прочие — точки подключения</t>
         </is>
       </c>
     </row>
@@ -6413,7 +6453,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Кухня столовой, прачечная: подключение оборудования</t>
+          <t>Трапы и лотки гаражей/эллинга, бензомаслоуловитель (ЛОС) 1 л/с</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -6425,10 +6465,10 @@
         <v>1</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>200000</v>
+        <v>600000</v>
       </c>
       <c r="F63" s="4">
-        <f>H63*0.5</f>
+        <f>H63*0.75</f>
         <v/>
       </c>
       <c r="G63" s="4">
@@ -6441,19 +6481,19 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>рынок</t>
+          <t>ВОЗ — обязательно</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>14 Вентиляция и кондиционирование (ОВК)</t>
+          <t>13 Водоснабжение и канализация (ВК)</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>П1/В1 проживание 1 300 м³/ч с рекуператором, воздуховоды, распределители</t>
+          <t>Кухня столовой, прачечная: подключение оборудования</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -6465,10 +6505,10 @@
         <v>1</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>2100000</v>
+        <v>200000</v>
       </c>
       <c r="F64" s="4">
-        <f>H64*0.7</f>
+        <f>H64*0.5</f>
         <v/>
       </c>
       <c r="G64" s="4">
@@ -6493,7 +6533,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>П2/В2 спортзал 1 200 м³/ч с рекуператором и охладителем</t>
+          <t>П1/В1 проживание 1 300 м³/ч с рекуператором, воздуховоды, распределители</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -6505,7 +6545,7 @@
         <v>1</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>1700000</v>
+        <v>2100000</v>
       </c>
       <c r="F65" s="4">
         <f>H65*0.7</f>
@@ -6521,7 +6561,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>по ТЗ спортзала</t>
+          <t>рынок</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6573,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>В3 гаражи и эллинг: вытяжка по датчикам CO/паров, клапаны</t>
+          <t>П2/В2 спортзал 1 200 м³/ч с рекуператором и охладителем</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -6545,7 +6585,7 @@
         <v>1</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>650000</v>
+        <v>1700000</v>
       </c>
       <c r="F66" s="4">
         <f>H66*0.7</f>
@@ -6561,7 +6601,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>без приточки</t>
+          <t>по ТЗ спортзала</t>
         </is>
       </c>
     </row>
@@ -6573,7 +6613,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Кондиционирование: мини-VRF 22 кВт — спортзал, столовая, КПП, охрана</t>
+          <t>В3 гаражи и эллинг: вытяжка по датчикам CO/паров, клапаны</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -6585,10 +6625,10 @@
         <v>1</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>1800000</v>
+        <v>650000</v>
       </c>
       <c r="F67" s="4">
-        <f>H67*0.75</f>
+        <f>H67*0.7</f>
         <v/>
       </c>
       <c r="G67" s="4">
@@ -6601,19 +6641,19 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>A — «условно» ЭП</t>
+          <t>без приточки</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>15 Электроснабжение и освещение (ЭОМ)</t>
+          <t>14 Вентиляция и кондиционирование (ОВК)</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>ВРУ/ГРЩ 100 А, учёт, АВР на ДГУ посёлка, щиты этажные</t>
+          <t>Кондиционирование: мини-VRF 22 кВт — спортзал, столовая, КПП, охрана</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -6625,7 +6665,7 @@
         <v>1</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>750000</v>
+        <v>1800000</v>
       </c>
       <c r="F68" s="4">
         <f>H68*0.75</f>
@@ -6641,7 +6681,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>Pр ≈ 60 кВт</t>
+          <t>A — «условно» ЭП</t>
         </is>
       </c>
     </row>
@@ -6653,22 +6693,22 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Кабельные сети, розетки, выключатели, освещение (светильники служебного стандарта)</t>
+          <t>ВРУ/ГРЩ 100 А в электрощитовой 013, учёт, АВР на генератор, щиты этажные</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>компл</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>961.54</v>
+        <v>1</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>3300</v>
+        <v>750000</v>
       </c>
       <c r="F69" s="4">
-        <f>H69*0.55</f>
+        <f>H69*0.75</f>
         <v/>
       </c>
       <c r="G69" s="4">
@@ -6681,7 +6721,7 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>A — 6,0 млн ЭП-сметы</t>
+          <t>Pр ≈ 60 кВт</t>
         </is>
       </c>
     </row>
@@ -6693,22 +6733,22 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Освещение спортзала и фасадов (архитектурное, к воде)</t>
+          <t>Кабельные сети, розетки, выключатели, освещение (светильники служебного стандарта)</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>компл</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>1</v>
+        <v>956.76</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>700000</v>
+        <v>3300</v>
       </c>
       <c r="F70" s="4">
-        <f>H70*0.75</f>
+        <f>H70*0.55</f>
         <v/>
       </c>
       <c r="G70" s="4">
@@ -6721,7 +6761,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>рынок</t>
+          <t>A — 6,0 млн ЭП-сметы</t>
         </is>
       </c>
     </row>
@@ -6733,22 +6773,22 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Зарядные станции 7,4 кВт с управлением нагрузкой</t>
+          <t>Освещение спортзала и фасадов (архитектурное, к воде)</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>компл</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>120000</v>
+        <v>700000</v>
       </c>
       <c r="F71" s="4">
-        <f>H71*0.8</f>
+        <f>H71*0.75</f>
         <v/>
       </c>
       <c r="G71" s="4">
@@ -6761,7 +6801,7 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>C — только кабельные трассы</t>
+          <t>рынок</t>
         </is>
       </c>
     </row>
@@ -6773,22 +6813,22 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Молниезащита, заземление, уравнивание потенциалов</t>
+          <t>Зарядные станции 7,4 кВт с управлением нагрузкой</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>компл</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>450000</v>
+        <v>120000</v>
       </c>
       <c r="F72" s="4">
-        <f>H72*0.6</f>
+        <f>H72*0.8</f>
         <v/>
       </c>
       <c r="G72" s="4">
@@ -6801,31 +6841,31 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>аналог 291-МЗ</t>
+          <t>C — только кабельные трассы</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>16 Слаботочные системы и пожарная безопасность (СС, ПБ)</t>
+          <t>15 Электроснабжение и освещение (ЭОМ)</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>АПС адресная + СОУЭ 2 типа</t>
+          <t>Молниезащита, заземление, уравнивание потенциалов</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>компл</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>961.54</v>
+        <v>1</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>650</v>
+        <v>450000</v>
       </c>
       <c r="F73" s="4">
         <f>H73*0.6</f>
@@ -6841,7 +6881,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>СП 484, 3.13130</t>
+          <t>аналог 291-МЗ</t>
         </is>
       </c>
     </row>
@@ -6853,22 +6893,22 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Модульное пожаротушение эллинга и котельной (по разделу ПБ)</t>
+          <t>АПС адресная + СОУЭ 2 типа</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>компл</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>1</v>
+        <v>956.76</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>400000</v>
+        <v>650</v>
       </c>
       <c r="F74" s="4">
-        <f>H74*0.8</f>
+        <f>H74*0.6</f>
         <v/>
       </c>
       <c r="G74" s="4">
@@ -6881,7 +6921,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>опция — проверить в ПБ</t>
+          <t>СП 484, 3.13130</t>
         </is>
       </c>
     </row>
@@ -6893,7 +6933,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>КПП: СКУД, шлагбаум, распознавание номеров, домофония</t>
+          <t>Модульное пожаротушение эллинга и котельной (по разделу ПБ)</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6905,10 +6945,10 @@
         <v>1</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>700000</v>
+        <v>400000</v>
       </c>
       <c r="F75" s="4">
-        <f>H75*0.75</f>
+        <f>H75*0.8</f>
         <v/>
       </c>
       <c r="G75" s="4">
@@ -6921,7 +6961,7 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>въезд посёлка</t>
+          <t>опция — проверить в ПБ</t>
         </is>
       </c>
     </row>
@@ -6933,7 +6973,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Видеонаблюдение 16 камер + сервер, охранная сигнализация</t>
+          <t>КПП: СКУД, шлагбаум, распознавание номеров, домофония</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6945,7 +6985,7 @@
         <v>1</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>650000</v>
+        <v>700000</v>
       </c>
       <c r="F76" s="4">
         <f>H76*0.75</f>
@@ -6961,7 +7001,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>рынок</t>
+          <t>въезд посёлка</t>
         </is>
       </c>
     </row>
@@ -6973,7 +7013,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>СКС, Wi-Fi, стойка, диспетчеризация инженерии (Home Assistant)</t>
+          <t>Видеонаблюдение 16 камер + сервер, охранная сигнализация</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6985,10 +7025,10 @@
         <v>1</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>550000</v>
+        <v>650000</v>
       </c>
       <c r="F77" s="4">
-        <f>H77*0.7</f>
+        <f>H77*0.75</f>
         <v/>
       </c>
       <c r="G77" s="4">
@@ -7001,7 +7041,7 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>аналог 291-СС</t>
+          <t>рынок</t>
         </is>
       </c>
     </row>
@@ -7013,7 +7053,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Пусконаладка всех инженерных систем</t>
+          <t>СКС, Wi-Fi, стойка, диспетчеризация инженерии (Home Assistant)</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -7025,10 +7065,10 @@
         <v>1</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>650000</v>
+        <v>550000</v>
       </c>
       <c r="F78" s="4">
-        <f>H78*0.0</f>
+        <f>H78*0.7</f>
         <v/>
       </c>
       <c r="G78" s="4">
@@ -7041,33 +7081,73 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
+          <t>аналог 291-СС</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>16 Слаботочные системы и пожарная безопасность (СС, ПБ)</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Пусконаладка всех инженерных систем</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>компл</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" s="4" t="n">
+        <v>650000</v>
+      </c>
+      <c r="F79" s="4">
+        <f>H79*0.0</f>
+        <v/>
+      </c>
+      <c r="G79" s="4">
+        <f>H79-F79</f>
+        <v/>
+      </c>
+      <c r="H79" s="4">
+        <f>D79*E79</f>
+        <v/>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
           <t>рынок</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="6" t="inlineStr"/>
-      <c r="B79" s="6" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr"/>
+      <c r="B80" s="6" t="inlineStr">
         <is>
           <t>ИТОГО СМР</t>
         </is>
       </c>
-      <c r="C79" s="6" t="inlineStr"/>
-      <c r="D79" s="10" t="inlineStr"/>
-      <c r="E79" s="7" t="inlineStr"/>
-      <c r="F79" s="7">
-        <f>SUM(F2:F78)</f>
-        <v/>
-      </c>
-      <c r="G79" s="7">
-        <f>SUM(G2:G78)</f>
-        <v/>
-      </c>
-      <c r="H79" s="7">
-        <f>SUM(H2:H78)</f>
-        <v/>
-      </c>
-      <c r="I79" s="6" t="inlineStr"/>
+      <c r="C80" s="6" t="inlineStr"/>
+      <c r="D80" s="10" t="inlineStr"/>
+      <c r="E80" s="7" t="inlineStr"/>
+      <c r="F80" s="7">
+        <f>SUM(F2:F79)</f>
+        <v/>
+      </c>
+      <c r="G80" s="7">
+        <f>SUM(G2:G79)</f>
+        <v/>
+      </c>
+      <c r="H80" s="7">
+        <f>SUM(H2:H79)</f>
+        <v/>
+      </c>
+      <c r="I80" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7080,7 +7160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I79"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7389,7 +7469,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Сваи ЖБ С80.30 (8 м) с забивкой, 77 шт.</t>
+          <t>Сваи ЖБ С80.30 (8 м) с забивкой, 82 шт.</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -7398,7 +7478,7 @@
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>31000</v>
@@ -7478,7 +7558,7 @@
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>513.5700000000001</v>
+        <v>513.1900000000001</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>700</v>
@@ -7518,7 +7598,7 @@
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>950</v>
@@ -7598,7 +7678,7 @@
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>154.1</v>
+        <v>154</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>25000</v>
@@ -7638,7 +7718,7 @@
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>513.5700000000001</v>
+        <v>513.1900000000001</v>
       </c>
       <c r="E14" s="4" t="n">
         <v>0</v>
@@ -7709,7 +7789,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Колонны 1 этажа: стальные с огнезащитой R150 (A) / монолит ЖБ 400×400 (B, C)</t>
+          <t>Колонны 1 этажа: стальные по ЭП с огнезащитой R150 (A) / монолит ЖБ 400×400 (B, C)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -7737,7 +7817,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>R150 для стали — 1,5–3 тыс./м² поверхности; ЖБ обеспечивает сам</t>
+          <t>в ЭП — металл; R150 для стали — 1,5–3 тыс./м² поверхности; ЖБ обеспечивает сам</t>
         </is>
       </c>
     </row>
@@ -7749,7 +7829,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Межэтажное и под плоскую кровлю: монолит ЖБ плита 200 + рёбра 600 (A, B) / ПБ + монолитные участки (C)</t>
+          <t>Перекрытие 1 этажа и под плоскую кровлю: монолит ЖБ ребристое, плита 250/200 (A, B) / ПБ + монолитные участки (C)</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -7758,7 +7838,7 @@
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>798.74</v>
+        <v>945.59</v>
       </c>
       <c r="E17" s="4" t="n">
         <v>6800</v>
@@ -7777,7 +7857,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>монолит 10,5–12,5 тыс.; ПБ 5,5–7 тыс.</t>
+          <t>по ЭП 660,5 м² плиты 250 + 285,1 м² плиты 200; монолит 10,5–12,5 тыс.</t>
         </is>
       </c>
     </row>
@@ -7798,7 +7878,7 @@
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>798.74</v>
+        <v>945.59</v>
       </c>
       <c r="E18" s="4" t="n">
         <v>0</v>
@@ -7909,7 +7989,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Наружные стены газобетон D500 400 мм (блок, клей, армирование, кладка)</t>
+          <t>Наружные стены газобетон D400 400 мм (блок, клей, армирование, кладка)</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -7918,7 +7998,7 @@
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>309.14</v>
+        <v>257.56</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>13000</v>
@@ -7958,7 +8038,7 @@
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>153.54</v>
+        <v>147.21</v>
       </c>
       <c r="E22" s="4" t="n">
         <v>13000</v>
@@ -7998,7 +8078,7 @@
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>57.47</v>
+        <v>44.25</v>
       </c>
       <c r="E23" s="4" t="n">
         <v>14000</v>
@@ -8078,7 +8158,7 @@
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>473.73</v>
+        <v>353.6</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>7000</v>
@@ -8109,7 +8189,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Скатная кровля: стропила, ОСП, мембраны, кликфальц, водосток, снегозадержание</t>
+          <t>Скатная кровля 10°: стропила, ОСП, мембраны, Кликфальц Pro, водосток, снегозадержание</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -8118,7 +8198,7 @@
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>570.9299999999999</v>
+        <v>448.03</v>
       </c>
       <c r="E26" s="4" t="n">
         <v>10000</v>
@@ -8149,7 +8229,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Плоская кровля: эксплуатируемая (A, B) / неэксплуатируемая (C)</t>
+          <t>Плоская кровля неэксплуатируемая: уклоны, утепление XPS 200, мембрана, примыкания</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -8158,7 +8238,7 @@
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>233.34</v>
+        <v>339.91</v>
       </c>
       <c r="E27" s="4" t="n">
         <v>8000</v>
@@ -8177,7 +8257,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>рынок 9–16 тыс.</t>
+          <t>по ЭП — неэксплуатируемая; рынок 7–10 тыс.</t>
         </is>
       </c>
     </row>
@@ -8189,7 +8269,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Каркасные фронтоны</t>
+          <t>Каркасные стены чердака (фронтоны) 200 мм с фальцем</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -8198,7 +8278,7 @@
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>186.21</v>
+        <v>51.72</v>
       </c>
       <c r="E28" s="4" t="n">
         <v>5500</v>
@@ -8629,7 +8709,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Ворота гаражные секционные утеплённые с автоматикой 3.5×2.6 м</t>
+          <t>Ворота гаражные секционные утеплённые с автоматикой (одинарные боксы) 3,5×2,6 м</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -8638,7 +8718,7 @@
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>200000</v>
@@ -8669,7 +8749,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Ворота эллинга подъёмно-секционные (под катер на прицепе) 4.5×3.6 м</t>
+          <t>Ворота гаражные секционные утеплённые с автоматикой (двойные боксы 004, 009) 5,5×2,6 м</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -8678,10 +8758,10 @@
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>520000</v>
+        <v>300000</v>
       </c>
       <c r="F40" s="4">
         <f>H40*0.85</f>
@@ -8697,7 +8777,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>нестандарт, усиленный привод</t>
+          <t>широкие, с приводом</t>
         </is>
       </c>
     </row>
@@ -8709,7 +8789,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Двери наружные металлические утеплённые</t>
+          <t>Ворота эллинга подъёмно-секционные (два катера на прицепах) 5,5×3,6 м</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -8718,13 +8798,13 @@
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>60000</v>
+        <v>580000</v>
       </c>
       <c r="F41" s="4">
-        <f>H41*0.8</f>
+        <f>H41*0.85</f>
         <v/>
       </c>
       <c r="G41" s="4">
@@ -8737,7 +8817,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>рынок МО</t>
+          <t>нестандарт, усиленный привод</t>
         </is>
       </c>
     </row>
@@ -8749,19 +8829,19 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Входная группа КПП (алюминий, домофон, доводчик)</t>
+          <t>Двери наружные металлические утеплённые</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>компл</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>280000</v>
+        <v>60000</v>
       </c>
       <c r="F42" s="4">
         <f>H42*0.8</f>
@@ -8784,12 +8864,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>09 Наружные МК</t>
+          <t>08 Окна, витражи, ворота</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Наружная эвакуационная лестница 3-го типа со 2 этажа</t>
+          <t>Входная группа КПП (алюминий, домофон, доводчик)</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -8801,10 +8881,10 @@
         <v>1</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>850000</v>
+        <v>280000</v>
       </c>
       <c r="F43" s="4">
-        <f>H43*0.7</f>
+        <f>H43*0.8</f>
         <v/>
       </c>
       <c r="G43" s="4">
@@ -8817,7 +8897,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>второй эвакуационный выход Ф1.2</t>
+          <t>рынок МО</t>
         </is>
       </c>
     </row>
@@ -8829,7 +8909,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Навесы, ограждения эксплуатируемой кровли, козырьки</t>
+          <t>Наружная эвакуационная лестница 3-го типа со 2 этажа</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -8841,7 +8921,7 @@
         <v>1</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>900000</v>
+        <v>850000</v>
       </c>
       <c r="F44" s="4">
         <f>H44*0.7</f>
@@ -8857,34 +8937,34 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>без спецификации — по ведомости архитектора</t>
+          <t>второй эвакуационный выход Ф1.2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>10 Отделка черновая</t>
+          <t>09 Наружные МК</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Техзона: упрочнённый пол (топпинг), обеспыливание стен и потолков, покраска</t>
+          <t>Навесы, козырьки, ограждения перехода и наружной лестницы</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>компл</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>379.01</v>
+        <v>1</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>3500</v>
+        <v>900000</v>
       </c>
       <c r="F45" s="4">
-        <f>H45*0.45</f>
+        <f>H45*0.7</f>
         <v/>
       </c>
       <c r="G45" s="4">
@@ -8897,7 +8977,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>A — единая ставка ЭП-сметы</t>
+          <t>без спецификации — по ведомости архитектора</t>
         </is>
       </c>
     </row>
@@ -8909,7 +8989,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Служебные, проживание, МОП: стяжка, штукатурка, ГКЛ, подготовка</t>
+          <t>Техзона: упрочнённый пол (топпинг), обеспыливание стен и потолков, покраска</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -8918,10 +8998,10 @@
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>473.38</v>
+        <v>382.32</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>9000</v>
+        <v>3500</v>
       </c>
       <c r="F46" s="4">
         <f>H46*0.45</f>
@@ -8937,7 +9017,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>рынок 8–14 тыс.</t>
+          <t>A — единая ставка ЭП-сметы</t>
         </is>
       </c>
     </row>
@@ -8949,7 +9029,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Спортзал: стяжка с виброразвязкой, акустическая подготовка</t>
+          <t>Служебные, проживание, МОП: стяжка, штукатурка, ГКЛ, подготовка</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -8958,13 +9038,13 @@
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>109.15</v>
+        <v>459.96</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>13000</v>
+        <v>9000</v>
       </c>
       <c r="F47" s="4">
-        <f>H47*0.5</f>
+        <f>H47*0.45</f>
         <v/>
       </c>
       <c r="G47" s="4">
@@ -8977,19 +9057,19 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>свободные веса</t>
+          <t>рынок 8–14 тыс.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>11 Отделка чистовая</t>
+          <t>10 Отделка черновая</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Техзона: разметка, отбойники, полимерные полы в эллинге и котельной</t>
+          <t>Спортзал: стяжка с виброразвязкой, акустическая подготовка</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -8998,13 +9078,13 @@
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>379.01</v>
+        <v>114.48</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>2000</v>
+        <v>13000</v>
       </c>
       <c r="F48" s="4">
-        <f>H48*0.6</f>
+        <f>H48*0.5</f>
         <v/>
       </c>
       <c r="G48" s="4">
@@ -9017,7 +9097,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>A — единая ставка ЭП</t>
+          <t>свободные веса</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9109,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Служебные и проживание: кварцвинил, керамогранит в с/у, покраска, Армстронг/натяжные, межкомнатные двери</t>
+          <t>Техзона: разметка, отбойники, полимерные полы в эллинге и котельной</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -9038,10 +9118,10 @@
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>473.38</v>
+        <v>382.32</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="F49" s="4">
         <f>H49*0.6</f>
@@ -9057,7 +9137,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>минимальный стандарт — решение 05.10; C — shell &amp; core</t>
+          <t>A — единая ставка ЭП</t>
         </is>
       </c>
     </row>
@@ -9069,7 +9149,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Спортзал: спортивное покрытие, акустика, зеркала, раздевалка</t>
+          <t>Служебные и проживание: кварцвинил, керамогранит в с/у, покраска, Армстронг/натяжные, межкомнатные двери</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -9078,13 +9158,13 @@
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>109.15</v>
+        <v>459.96</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>32000</v>
+        <v>0</v>
       </c>
       <c r="F50" s="4">
-        <f>H50*0.65</f>
+        <f>H50*0.6</f>
         <v/>
       </c>
       <c r="G50" s="4">
@@ -9097,7 +9177,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>по ТЗ интересантов, без лимита</t>
+          <t>минимальный стандарт — решение 05.10; C — shell &amp; core</t>
         </is>
       </c>
     </row>
@@ -9109,22 +9189,22 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Внутренние ограждения, поручни, техметаллоизделия</t>
+          <t>Спортзал: спортивное покрытие, акустика, зеркала, раздевалка</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>компл</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>1</v>
+        <v>114.48</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>900000</v>
+        <v>32000</v>
       </c>
       <c r="F51" s="4">
-        <f>H51*0.7</f>
+        <f>H51*0.65</f>
         <v/>
       </c>
       <c r="G51" s="4">
@@ -9137,19 +9217,19 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>рынок МО</t>
+          <t>по ТЗ интересантов, без лимита</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>12 Отопление (ОВ)</t>
+          <t>11 Отделка чистовая</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Котельная: пеллетный котёл 60 кВт + бункер, электрокотёл 24 кВт, буфер 1 000 л, обвязка, автоматика (Qрасч ≈ 61 кВт)</t>
+          <t>Внутренние ограждения, поручни, техметаллоизделия</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -9161,10 +9241,10 @@
         <v>1</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>2300000</v>
+        <v>900000</v>
       </c>
       <c r="F52" s="4">
-        <f>H52*0.75</f>
+        <f>H52*0.7</f>
         <v/>
       </c>
       <c r="G52" s="4">
@@ -9177,7 +9257,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>аналог 291-ОВ «Ромарио»</t>
+          <t>рынок МО</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9269,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Дымоход нержавеющий утеплённый Ø200, h ≈ 11 м</t>
+          <t>Котельная: пеллетный котёл 60 кВт + бункер, электрокотёл 24 кВт, буфер 1 000 л, обвязка, автоматика (Qрасч ≈ 62 кВт)</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -9201,7 +9281,7 @@
         <v>1</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>250000</v>
+        <v>2300000</v>
       </c>
       <c r="F53" s="4">
         <f>H53*0.75</f>
@@ -9217,7 +9297,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>рынок</t>
+          <t>аналог 291-ОВ «Ромарио»</t>
         </is>
       </c>
     </row>
@@ -9229,22 +9309,22 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Тёплые полы водяные: проживание, МОП, спортзал</t>
+          <t>Дымоход нержавеющий утеплённый Ø200, h ≈ 11 м</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>компл</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>522.53</v>
+        <v>1</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>2300</v>
+        <v>250000</v>
       </c>
       <c r="F54" s="4">
-        <f>H54*0.5</f>
+        <f>H54*0.75</f>
         <v/>
       </c>
       <c r="G54" s="4">
@@ -9257,7 +9337,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>рынок МО</t>
+          <t>рынок</t>
         </is>
       </c>
     </row>
@@ -9269,22 +9349,22 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Конвекторы внутрипольные у витражей, радиаторы в с/у и КПП</t>
+          <t>Тёплые полы водяные: проживание, МОП, спортзал</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>28</v>
+        <v>514.4400000000001</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>32000</v>
+        <v>2300</v>
       </c>
       <c r="F55" s="4">
-        <f>H55*0.75</f>
+        <f>H55*0.5</f>
         <v/>
       </c>
       <c r="G55" s="4">
@@ -9297,7 +9377,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>рынок</t>
+          <t>рынок МО</t>
         </is>
       </c>
     </row>
@@ -9309,7 +9389,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Воздушно-отопительные агрегаты гаражей и эллинга (+5 °C)</t>
+          <t>Конвекторы внутрипольные у витражей, радиаторы в с/у и КПП</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -9318,10 +9398,10 @@
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>95000</v>
+        <v>32000</v>
       </c>
       <c r="F56" s="4">
         <f>H56*0.75</f>
@@ -9337,7 +9417,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Volcano/аналог</t>
+          <t>рынок</t>
         </is>
       </c>
     </row>
@@ -9349,22 +9429,22 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Магистрали, коллекторы, изоляция, ПНР</t>
+          <t>Воздушно-отопительные агрегаты гаражей и эллинга (+5 °C)</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>компл</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>800000</v>
+        <v>95000</v>
       </c>
       <c r="F57" s="4">
-        <f>H57*0.55</f>
+        <f>H57*0.75</f>
         <v/>
       </c>
       <c r="G57" s="4">
@@ -9377,19 +9457,19 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>рынок</t>
+          <t>Volcano/аналог</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>13 Водоснабжение и канализация (ВК)</t>
+          <t>12 Отопление (ОВ)</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Узел ввода, учёт, фильтрация/умягчение</t>
+          <t>Магистрали, коллекторы, изоляция, ПНР</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -9401,10 +9481,10 @@
         <v>1</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>380000</v>
+        <v>800000</v>
       </c>
       <c r="F58" s="4">
-        <f>H58*0.75</f>
+        <f>H58*0.55</f>
         <v/>
       </c>
       <c r="G58" s="4">
@@ -9417,7 +9497,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>посёлковая сеть</t>
+          <t>рынок</t>
         </is>
       </c>
     </row>
@@ -9429,7 +9509,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Бойлер косвенного нагрева 500 л + рециркуляция ГВС</t>
+          <t>Узел ввода, учёт, фильтрация/умягчение</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -9441,7 +9521,7 @@
         <v>1</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>330000</v>
+        <v>380000</v>
       </c>
       <c r="F59" s="4">
         <f>H59*0.75</f>
@@ -9457,7 +9537,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>рынок</t>
+          <t>посёлковая сеть</t>
         </is>
       </c>
     </row>
@@ -9469,22 +9549,22 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Внутренние сети В1/Т3/Т4/К1 с изоляцией</t>
+          <t>Бойлер косвенного нагрева 500 л + рециркуляция ГВС</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>компл</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>961.54</v>
+        <v>1</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>1000</v>
+        <v>330000</v>
       </c>
       <c r="F60" s="4">
-        <f>H60*0.5</f>
+        <f>H60*0.75</f>
         <v/>
       </c>
       <c r="G60" s="4">
@@ -9497,7 +9577,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>рынок МО</t>
+          <t>рынок</t>
         </is>
       </c>
     </row>
@@ -9509,22 +9589,22 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Санузлы: унитаз, раковина, душ/поддон, смесители — 10 шт.</t>
+          <t>Внутренние сети В1/Т3/Т4/К1 с изоляцией</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>10</v>
+        <v>956.76</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>60000</v>
+        <v>1000</v>
       </c>
       <c r="F61" s="4">
-        <f>H61*0.7</f>
+        <f>H61*0.5</f>
         <v/>
       </c>
       <c r="G61" s="4">
@@ -9537,7 +9617,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>C — только КПП и раздевалка, прочие — точки подключения</t>
+          <t>рынок МО</t>
         </is>
       </c>
     </row>
@@ -9549,22 +9629,22 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Трапы и лотки гаражей/эллинга, бензомаслоуловитель (ЛОС) 1 л/с</t>
+          <t>Санузлы: унитаз, раковина, душ/поддон, смесители — 10 шт.</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>компл</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>600000</v>
+        <v>60000</v>
       </c>
       <c r="F62" s="4">
-        <f>H62*0.75</f>
+        <f>H62*0.7</f>
         <v/>
       </c>
       <c r="G62" s="4">
@@ -9577,7 +9657,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>ВОЗ — обязательно</t>
+          <t>C — только КПП и раздевалка, прочие — точки подключения</t>
         </is>
       </c>
     </row>
@@ -9589,7 +9669,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Кухня столовой, прачечная: подключение оборудования</t>
+          <t>Трапы и лотки гаражей/эллинга, бензомаслоуловитель (ЛОС) 1 л/с</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -9601,10 +9681,10 @@
         <v>1</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>150000</v>
+        <v>600000</v>
       </c>
       <c r="F63" s="4">
-        <f>H63*0.5</f>
+        <f>H63*0.75</f>
         <v/>
       </c>
       <c r="G63" s="4">
@@ -9617,19 +9697,19 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>рынок</t>
+          <t>ВОЗ — обязательно</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>14 Вентиляция и кондиционирование (ОВК)</t>
+          <t>13 Водоснабжение и канализация (ВК)</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>П1/В1 проживание 1 300 м³/ч с рекуператором, воздуховоды, распределители</t>
+          <t>Кухня столовой, прачечная: подключение оборудования</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -9641,10 +9721,10 @@
         <v>1</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>1200000</v>
+        <v>150000</v>
       </c>
       <c r="F64" s="4">
-        <f>H64*0.7</f>
+        <f>H64*0.5</f>
         <v/>
       </c>
       <c r="G64" s="4">
@@ -9669,7 +9749,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>П2/В2 спортзал 1 200 м³/ч с рекуператором и охладителем</t>
+          <t>П1/В1 проживание 1 300 м³/ч с рекуператором, воздуховоды, распределители</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -9681,7 +9761,7 @@
         <v>1</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>1700000</v>
+        <v>1200000</v>
       </c>
       <c r="F65" s="4">
         <f>H65*0.7</f>
@@ -9697,7 +9777,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>по ТЗ спортзала</t>
+          <t>рынок</t>
         </is>
       </c>
     </row>
@@ -9709,7 +9789,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>В3 гаражи и эллинг: вытяжка по датчикам CO/паров, клапаны</t>
+          <t>П2/В2 спортзал 1 200 м³/ч с рекуператором и охладителем</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -9721,7 +9801,7 @@
         <v>1</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>650000</v>
+        <v>1700000</v>
       </c>
       <c r="F66" s="4">
         <f>H66*0.7</f>
@@ -9737,7 +9817,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>без приточки</t>
+          <t>по ТЗ спортзала</t>
         </is>
       </c>
     </row>
@@ -9749,7 +9829,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Кондиционирование: мини-VRF 22 кВт — спортзал, столовая, КПП, охрана</t>
+          <t>В3 гаражи и эллинг: вытяжка по датчикам CO/паров, клапаны</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -9761,10 +9841,10 @@
         <v>1</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>1500000</v>
+        <v>650000</v>
       </c>
       <c r="F67" s="4">
-        <f>H67*0.75</f>
+        <f>H67*0.7</f>
         <v/>
       </c>
       <c r="G67" s="4">
@@ -9777,19 +9857,19 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>A — «условно» ЭП</t>
+          <t>без приточки</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>15 Электроснабжение и освещение (ЭОМ)</t>
+          <t>14 Вентиляция и кондиционирование (ОВК)</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>ВРУ/ГРЩ 100 А, учёт, АВР на ДГУ посёлка, щиты этажные</t>
+          <t>Кондиционирование: мини-VRF 22 кВт — спортзал, столовая, КПП, охрана</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -9801,7 +9881,7 @@
         <v>1</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>750000</v>
+        <v>1500000</v>
       </c>
       <c r="F68" s="4">
         <f>H68*0.75</f>
@@ -9817,7 +9897,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>Pр ≈ 60 кВт</t>
+          <t>A — «условно» ЭП</t>
         </is>
       </c>
     </row>
@@ -9829,22 +9909,22 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Кабельные сети, розетки, выключатели, освещение (светильники служебного стандарта)</t>
+          <t>ВРУ/ГРЩ 100 А в электрощитовой 013, учёт, АВР на генератор, щиты этажные</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>компл</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>961.54</v>
+        <v>1</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>2600</v>
+        <v>750000</v>
       </c>
       <c r="F69" s="4">
-        <f>H69*0.55</f>
+        <f>H69*0.75</f>
         <v/>
       </c>
       <c r="G69" s="4">
@@ -9857,7 +9937,7 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>A — 6,0 млн ЭП-сметы</t>
+          <t>Pр ≈ 60 кВт</t>
         </is>
       </c>
     </row>
@@ -9869,22 +9949,22 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Освещение спортзала и фасадов (архитектурное, к воде)</t>
+          <t>Кабельные сети, розетки, выключатели, освещение (светильники служебного стандарта)</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>компл</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>1</v>
+        <v>956.76</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>500000</v>
+        <v>2600</v>
       </c>
       <c r="F70" s="4">
-        <f>H70*0.75</f>
+        <f>H70*0.55</f>
         <v/>
       </c>
       <c r="G70" s="4">
@@ -9897,7 +9977,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>рынок</t>
+          <t>A — 6,0 млн ЭП-сметы</t>
         </is>
       </c>
     </row>
@@ -9909,22 +9989,22 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Зарядные станции 7,4 кВт с управлением нагрузкой</t>
+          <t>Освещение спортзала и фасадов (архитектурное, к воде)</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>компл</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="F71" s="4">
-        <f>H71*0.8</f>
+        <f>H71*0.75</f>
         <v/>
       </c>
       <c r="G71" s="4">
@@ -9937,7 +10017,7 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>C — только кабельные трассы</t>
+          <t>рынок</t>
         </is>
       </c>
     </row>
@@ -9949,22 +10029,22 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Молниезащита, заземление, уравнивание потенциалов</t>
+          <t>Зарядные станции 7,4 кВт с управлением нагрузкой</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>компл</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>450000</v>
+        <v>0</v>
       </c>
       <c r="F72" s="4">
-        <f>H72*0.6</f>
+        <f>H72*0.8</f>
         <v/>
       </c>
       <c r="G72" s="4">
@@ -9977,31 +10057,31 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>аналог 291-МЗ</t>
+          <t>C — только кабельные трассы</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>16 Слаботочные системы и пожарная безопасность (СС, ПБ)</t>
+          <t>15 Электроснабжение и освещение (ЭОМ)</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>АПС адресная + СОУЭ 2 типа</t>
+          <t>Молниезащита, заземление, уравнивание потенциалов</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>компл</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>961.54</v>
+        <v>1</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>650</v>
+        <v>450000</v>
       </c>
       <c r="F73" s="4">
         <f>H73*0.6</f>
@@ -10017,7 +10097,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>СП 484, 3.13130</t>
+          <t>аналог 291-МЗ</t>
         </is>
       </c>
     </row>
@@ -10029,22 +10109,22 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Модульное пожаротушение эллинга и котельной (по разделу ПБ)</t>
+          <t>АПС адресная + СОУЭ 2 типа</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>компл</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>1</v>
+        <v>956.76</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>400000</v>
+        <v>650</v>
       </c>
       <c r="F74" s="4">
-        <f>H74*0.8</f>
+        <f>H74*0.6</f>
         <v/>
       </c>
       <c r="G74" s="4">
@@ -10057,7 +10137,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>опция — проверить в ПБ</t>
+          <t>СП 484, 3.13130</t>
         </is>
       </c>
     </row>
@@ -10069,7 +10149,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>КПП: СКУД, шлагбаум, распознавание номеров, домофония</t>
+          <t>Модульное пожаротушение эллинга и котельной (по разделу ПБ)</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -10081,10 +10161,10 @@
         <v>1</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>600000</v>
+        <v>400000</v>
       </c>
       <c r="F75" s="4">
-        <f>H75*0.75</f>
+        <f>H75*0.8</f>
         <v/>
       </c>
       <c r="G75" s="4">
@@ -10097,7 +10177,7 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>въезд посёлка</t>
+          <t>опция — проверить в ПБ</t>
         </is>
       </c>
     </row>
@@ -10109,7 +10189,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Видеонаблюдение 16 камер + сервер, охранная сигнализация</t>
+          <t>КПП: СКУД, шлагбаум, распознавание номеров, домофония</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -10137,7 +10217,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>рынок</t>
+          <t>въезд посёлка</t>
         </is>
       </c>
     </row>
@@ -10149,7 +10229,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>СКС, Wi-Fi, стойка, диспетчеризация инженерии (Home Assistant)</t>
+          <t>Видеонаблюдение 16 камер + сервер, охранная сигнализация</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -10161,10 +10241,10 @@
         <v>1</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>400000</v>
+        <v>600000</v>
       </c>
       <c r="F77" s="4">
-        <f>H77*0.7</f>
+        <f>H77*0.75</f>
         <v/>
       </c>
       <c r="G77" s="4">
@@ -10177,7 +10257,7 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>аналог 291-СС</t>
+          <t>рынок</t>
         </is>
       </c>
     </row>
@@ -10189,7 +10269,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Пусконаладка всех инженерных систем</t>
+          <t>СКС, Wi-Fi, стойка, диспетчеризация инженерии (Home Assistant)</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -10201,10 +10281,10 @@
         <v>1</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>550000</v>
+        <v>400000</v>
       </c>
       <c r="F78" s="4">
-        <f>H78*0.0</f>
+        <f>H78*0.7</f>
         <v/>
       </c>
       <c r="G78" s="4">
@@ -10217,33 +10297,73 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
+          <t>аналог 291-СС</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>16 Слаботочные системы и пожарная безопасность (СС, ПБ)</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Пусконаладка всех инженерных систем</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>компл</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" s="4" t="n">
+        <v>550000</v>
+      </c>
+      <c r="F79" s="4">
+        <f>H79*0.0</f>
+        <v/>
+      </c>
+      <c r="G79" s="4">
+        <f>H79-F79</f>
+        <v/>
+      </c>
+      <c r="H79" s="4">
+        <f>D79*E79</f>
+        <v/>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
           <t>рынок</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="6" t="inlineStr"/>
-      <c r="B79" s="6" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr"/>
+      <c r="B80" s="6" t="inlineStr">
         <is>
           <t>ИТОГО СМР</t>
         </is>
       </c>
-      <c r="C79" s="6" t="inlineStr"/>
-      <c r="D79" s="10" t="inlineStr"/>
-      <c r="E79" s="7" t="inlineStr"/>
-      <c r="F79" s="7">
-        <f>SUM(F2:F78)</f>
-        <v/>
-      </c>
-      <c r="G79" s="7">
-        <f>SUM(G2:G78)</f>
-        <v/>
-      </c>
-      <c r="H79" s="7">
-        <f>SUM(H2:H78)</f>
-        <v/>
-      </c>
-      <c r="I79" s="6" t="inlineStr"/>
+      <c r="C80" s="6" t="inlineStr"/>
+      <c r="D80" s="10" t="inlineStr"/>
+      <c r="E80" s="7" t="inlineStr"/>
+      <c r="F80" s="7">
+        <f>SUM(F2:F79)</f>
+        <v/>
+      </c>
+      <c r="G80" s="7">
+        <f>SUM(G2:G79)</f>
+        <v/>
+      </c>
+      <c r="H80" s="7">
+        <f>SUM(H2:H79)</f>
+        <v/>
+      </c>
+      <c r="I80" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10256,7 +10376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -10619,7 +10739,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Мебель и техника: 13 спален, столовая, кухня управляющего, охрана, КПП</t>
+          <t>Мебель и техника: 14 спален, столовая, квартира управляющего, охрана, КПП</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
@@ -10671,19 +10791,45 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Сборный понтон 2×(3×12 м) с трапом и швартовкой (база ГИМС)</t>
+          <t>Слип для спуска катеров (по генплану ЭП), монолит ЖБ ≈ 6×20 м</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>5500000</v>
+        <v>2500000</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>4500000</v>
+        <v>2000000</v>
       </c>
       <c r="E16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>прибрежная полоса — согласование</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>24 Причал (вне здания)</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Сборный понтон 2×(3×12 м) с трапом и швартовкой (база ГИМС)</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>не регистрируется; зимой лежит на дне</t>
         </is>
@@ -10753,7 +10899,7 @@
         <v>1420000</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>1477</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="3">
@@ -10772,7 +10918,7 @@
         <v>896400</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>932</v>
+        <v>937</v>
       </c>
     </row>
     <row r="4">
@@ -10782,16 +10928,16 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>13254324</v>
+        <v>13417274</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>8438449</v>
+        <v>8589733</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>8438449</v>
+        <v>8589733</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>8776</v>
+        <v>8978</v>
       </c>
     </row>
     <row r="5">
@@ -10801,16 +10947,16 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>14774376</v>
+        <v>17068111</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>11895510</v>
+        <v>13867962</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>8141432</v>
+        <v>9140012</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>12371</v>
+        <v>14495</v>
       </c>
     </row>
     <row r="6">
@@ -10820,16 +10966,16 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>7558230</v>
+        <v>6578145</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>7269420</v>
+        <v>6331510</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>7269420</v>
+        <v>6331510</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>7560</v>
+        <v>6618</v>
       </c>
     </row>
     <row r="7">
@@ -10839,16 +10985,16 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>14104128</v>
+        <v>10871960</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>13537245</v>
+        <v>10407270</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>11916285</v>
+        <v>9959240</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>14079</v>
+        <v>10878</v>
       </c>
     </row>
     <row r="8">
@@ -10867,7 +11013,7 @@
         <v>12401000</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>13190</v>
+        <v>13256</v>
       </c>
     </row>
     <row r="9">
@@ -10877,16 +11023,16 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>10937720</v>
+        <v>10707720</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>8206000</v>
+        <v>8046000</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>7815360</v>
+        <v>7675360</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>8534</v>
+        <v>8410</v>
       </c>
     </row>
     <row r="10">
@@ -10896,16 +11042,16 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>3150000</v>
+        <v>2750000</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2350000</v>
+        <v>2050000</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>1750000</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2444</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="11">
@@ -10915,16 +11061,16 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>10961556</v>
+        <v>10907064</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>7119608</v>
+        <v>7080696</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>7005905</v>
+        <v>6966000</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>7404</v>
+        <v>7401</v>
       </c>
     </row>
     <row r="12">
@@ -10934,16 +11080,16 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>24932729</v>
+        <v>24818726</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>12267645</v>
+        <v>12258600</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>5150820</v>
+        <v>5328000</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>12758</v>
+        <v>12813</v>
       </c>
     </row>
     <row r="13">
@@ -10953,16 +11099,16 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>7258578</v>
+        <v>7237544</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>6117819</v>
+        <v>6099212</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>6017819</v>
+        <v>5999212</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>6363</v>
+        <v>6375</v>
       </c>
     </row>
     <row r="14">
@@ -10972,16 +11118,16 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>4580002</v>
+        <v>4573788</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>3667694</v>
+        <v>3662436</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3021540</v>
+        <v>3016760</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>3814</v>
+        <v>3828</v>
       </c>
     </row>
     <row r="15">
@@ -11000,7 +11146,7 @@
         <v>5050000</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>6500</v>
+        <v>6532</v>
       </c>
     </row>
     <row r="16">
@@ -11010,16 +11156,16 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>6994622</v>
+        <v>6974068</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>5553082</v>
+        <v>5537308</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>4200004</v>
+        <v>4187576</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>5775</v>
+        <v>5788</v>
       </c>
     </row>
     <row r="17">
@@ -11029,16 +11175,16 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>4871155</v>
+        <v>4867570</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>3575001</v>
+        <v>3571894</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>3175001</v>
+        <v>3171894</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>3718</v>
+        <v>3733</v>
       </c>
     </row>
   </sheetData>
@@ -11052,7 +11198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -11061,56 +11207,63 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Площади помещений — по экспликациям АР-концепта: 1 этаж ред. 01.09 (416,33 м²), 2 этаж ред. 31.07 (545,21 м²), итого 961,54 м². Смета ЭП считала 964,60 м² (иная редакция) — разница 0,3 %.</t>
+          <t>Площади помещений — по экспликациям финального ЭП от 23.10.2026: 1 этаж 420,04 м², 2 этаж 536,72 м², итого 956,76 м² (ТЭП); площадь застройки 490 м².</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Объёмы конструкций (перекрытия, кладка, кровли, фасады, остекление) — из сметы ЭП, лист «Исходные данные».</t>
+          <t>Объёмы конструкций — по листу 2.34 «Ведомости» финального ЭП: перекрытия, кладка, кровли, фронтоны, фасады, окна ПВХ.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Высоты этажей: 1 этаж 4,30 м (гаражи, ворота 2,6 м, катер на прицепе), 2 этаж 3,10 м; конёк +10,73.</t>
+          <t>Площадь алюминиевых витражей в ЭП не указана (только высота 4 750 мм) — принята 170,64 м² из предварительной сметы ЭП, уточнить у архитектора.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ворота: 8 гаражных 3,5×2,6 м и 1 эллинговые 4,5×3,6 м — размеры по сетке осей (шаг 4 475 + 825), уточнить по ведомости проёмов архитектора.</t>
+          <t>Высоты: 2 этаж на отметке +4,020, карниз ≈ +7,4, конёк +10,333; уклон скатной кровли 10°.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Геологии на пятне нет. Принят суглинок/глина ≈ 3 м по данным совещания 05.10 и ИГИ участков; несущая способность сваи 380 кН — до испытаний.</t>
+          <t>Ворота: 4 одинарных бокса 3,5×2,6 м, 2 двойных бокса 5,5×2,6 м, эллинг на два катера 5,5×3,6 м — размеры в ЭП не указаны, уточнить по ведомости проёмов.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Газа нет до 2028 г.; основной источник тепла — пеллеты с резервным электрокотлом, переход на газ заложен (как в доме «Ромарио»).</t>
+          <t>Несущие колонны 1 этажа в ЭП — металлические. В сценариях B и C заложена замена на монолитные ЖБ 400×400 (огнестойкость R150 над стоянкой без огнезащиты); в A — сталь с огнезащитой R150.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Цены — Москва и МО, IV кв. 2026, с НДС, «под ключ» (материал + работа + доставка + накладные подрядчика).</t>
+          <t>Геологии на пятне нет. Принят суглинок/глина ≈ 3 м по данным совещания 05.10 и ИГИ участков; несущая способность сваи 380 кН — до испытаний.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Файл по ссылке Dropbox от 23.10.2026 из окружения недоступен (хост заблокирован сетевой политикой) — при его получении сверить экспликацию, проёмы и ворота (см. записку).</t>
+          <t>Газа нет до 2028 г.; основной источник тепла — пеллеты с резервным электрокотлом, переход на газ заложен (как в доме «Ромарио»).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Цены — Москва и МО, IV кв. 2026, с НДС, «под ключ» (материал + работа + доставка + накладные подрядчика).</t>
         </is>
       </c>
     </row>

--- a/Берта Эллинг/12_Смета/БЭ-СМ Смета эллинга — 3 сценария.xlsx
+++ b/Берта Эллинг/12_Смета/БЭ-СМ Смета эллинга — 3 сценария.xlsx
@@ -1517,7 +1517,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Монолитная лестница 012 с ограждением</t>
+          <t>Монолитная лестница 010 с ограждением</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2126,7 +2126,7 @@
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E35" s="4" t="n">
         <v>9000</v>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>периметр ≈ 104 м</t>
+          <t>периметр ≈ 110 м (план 33,7 × 36,8 м)</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4733,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Монолитная лестница 012 с ограждением</t>
+          <t>Монолитная лестница 010 с ограждением</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -5342,7 +5342,7 @@
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E35" s="4" t="n">
         <v>8000</v>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>периметр ≈ 104 м</t>
+          <t>периметр ≈ 110 м (план 33,7 × 36,8 м)</t>
         </is>
       </c>
     </row>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Монолитная лестница 012 с ограждением</t>
+          <t>Монолитная лестница 010 с ограждением</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -8558,7 +8558,7 @@
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E35" s="4" t="n">
         <v>8000</v>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>периметр ≈ 104 м</t>
+          <t>периметр ≈ 110 м (план 33,7 × 36,8 м)</t>
         </is>
       </c>
     </row>
@@ -11004,16 +11004,16 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>14817000</v>
+        <v>14871000</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>12683000</v>
+        <v>12731000</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>12401000</v>
+        <v>12449000</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>13256</v>
+        <v>13306</v>
       </c>
     </row>
     <row r="9">
